--- a/output/roomself_excel/5109.xlsx
+++ b/output/roomself_excel/5109.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>202050</v>
+        <v>64277</v>
       </c>
       <c r="D2" t="n">
-        <v>3948</v>
+        <v>2216</v>
       </c>
       <c r="E2" t="n">
-        <v>1046</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>132349</v>
+        <v>202050</v>
       </c>
       <c r="D3" t="n">
-        <v>3080</v>
+        <v>3948</v>
       </c>
       <c r="E3" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2494</v>
+        <v>132349</v>
       </c>
       <c r="D4" t="n">
-        <v>404</v>
+        <v>3080</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,14 +532,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2322</v>
+        <v>68880</v>
       </c>
       <c r="D5" t="n">
-        <v>388</v>
+        <v>2164</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3354</v>
+        <v>68040</v>
       </c>
       <c r="D6" t="n">
-        <v>484</v>
+        <v>2136</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -576,14 +576,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2537</v>
+        <v>77227</v>
       </c>
       <c r="D7" t="n">
-        <v>408</v>
+        <v>2964</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2365</v>
+        <v>2494</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24017</v>
+        <v>2322</v>
       </c>
       <c r="D9" t="n">
-        <v>1248</v>
+        <v>388</v>
       </c>
       <c r="E9" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68880</v>
+        <v>3354</v>
       </c>
       <c r="D10" t="n">
-        <v>2164</v>
+        <v>484</v>
       </c>
       <c r="E10" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>77227</v>
+        <v>2537</v>
       </c>
       <c r="D11" t="n">
-        <v>2964</v>
+        <v>408</v>
       </c>
       <c r="E11" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -686,14 +686,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>64277</v>
+        <v>2365</v>
       </c>
       <c r="D12" t="n">
-        <v>2216</v>
+        <v>392</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1650</v>
+        <v>24017</v>
       </c>
       <c r="D13" t="n">
-        <v>332</v>
+        <v>1248</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2444</v>
+        <v>1650</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>332</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1325</v>
+        <v>2444</v>
       </c>
       <c r="D15" t="n">
-        <v>312</v>
+        <v>396</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68040</v>
+        <v>1325</v>
       </c>
       <c r="D16" t="n">
-        <v>2136</v>
+        <v>312</v>
       </c>
       <c r="E16" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5109.xlsx
+++ b/output/roomself_excel/5109.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>2216</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>3948</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>3080</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +513,6 @@
       <c r="D5" t="n">
         <v>2164</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>2136</v>
       </c>
-      <c r="E6" t="n">
-        <v>25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>2964</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>404</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>388</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>484</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>408</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>392</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>1248</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +657,6 @@
       <c r="D14" t="n">
         <v>332</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +673,6 @@
       <c r="D15" t="n">
         <v>396</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -782,12 +688,6 @@
       </c>
       <c r="D16" t="n">
         <v>312</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/5109.xlsx
+++ b/output/roomself_excel/5109.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
